--- a/backend/templates/template_site.xlsx
+++ b/backend/templates/template_site.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -37,13 +37,8 @@
       <color rgb="007B3F00"/>
       <sz val="11"/>
     </font>
-    <font>
-      <i val="1"/>
-      <color rgb="00375623"/>
-      <sz val="10"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill/>
     </fill>
@@ -60,13 +55,8 @@
         <fgColor rgb="00FFE699"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00E2EFDA"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="6">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -88,55 +78,11 @@
         <color rgb="00BFBFBF"/>
       </bottom>
     </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="thin">
-        <color rgb="00BFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="00BFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00BFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -144,11 +90,6 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -517,7 +458,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y3"/>
+  <dimension ref="A1:Y2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -674,137 +615,155 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="28" customHeight="1">
+    <row r="2">
       <c r="A2" s="3" t="inlineStr">
         <is>
-          <t>Ghi chu: Cot mau VANG la bat buoc. Tinh phai khop voi danh sach tinh trong he thong. Lat: 8.33-23.39, Long: 102.14-109.47 (Vietnam). Tram 2G/3G/4G/5G/Repeater/Booster: nhap 'x' neu co. MORAN: 'VNPT HOST' hoac 'MBF HOST'.</t>
-        </is>
-      </c>
-      <c r="B2" s="4" t="n"/>
-      <c r="C2" s="4" t="n"/>
-      <c r="D2" s="4" t="n"/>
-      <c r="E2" s="4" t="n"/>
-      <c r="F2" s="4" t="n"/>
-      <c r="G2" s="4" t="n"/>
-      <c r="H2" s="4" t="n"/>
-      <c r="I2" s="4" t="n"/>
-      <c r="J2" s="4" t="n"/>
-      <c r="K2" s="4" t="n"/>
-      <c r="L2" s="4" t="n"/>
-      <c r="M2" s="4" t="n"/>
-      <c r="N2" s="4" t="n"/>
-      <c r="O2" s="4" t="n"/>
-      <c r="P2" s="4" t="n"/>
-      <c r="Q2" s="4" t="n"/>
-      <c r="R2" s="4" t="n"/>
-      <c r="S2" s="4" t="n"/>
-      <c r="T2" s="4" t="n"/>
-      <c r="U2" s="4" t="n"/>
-      <c r="V2" s="4" t="n"/>
-      <c r="W2" s="4" t="n"/>
-      <c r="X2" s="4" t="n"/>
-      <c r="Y2" s="5" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="6" t="inlineStr">
-        <is>
           <t>MB</t>
         </is>
       </c>
-      <c r="B3" s="6" t="inlineStr">
+      <c r="B2" s="3" t="inlineStr">
         <is>
           <t>Ha Noi</t>
         </is>
       </c>
-      <c r="C3" s="6" t="inlineStr">
+      <c r="C2" s="3" t="inlineStr">
         <is>
           <t>Phuong Trung Hoa</t>
         </is>
       </c>
-      <c r="D3" s="6" t="inlineStr">
+      <c r="D2" s="3" t="inlineStr">
         <is>
           <t>HN-001-OLD</t>
         </is>
       </c>
-      <c r="E3" s="6" t="inlineStr">
+      <c r="E2" s="3" t="inlineStr">
         <is>
           <t>HN-001</t>
         </is>
       </c>
-      <c r="F3" s="6" t="inlineStr">
+      <c r="F2" s="3" t="inlineStr">
         <is>
           <t>VIP</t>
         </is>
       </c>
-      <c r="G3" s="6" t="n">
+      <c r="G2" s="3" t="n">
         <v>21.0285</v>
       </c>
-      <c r="H3" s="6" t="n">
+      <c r="H2" s="3" t="n">
         <v>105.8542</v>
       </c>
-      <c r="I3" s="6" t="inlineStr">
+      <c r="I2" s="3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="J3" s="6" t="inlineStr">
+      <c r="J2" s="3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="K3" s="6" t="inlineStr">
+      <c r="K2" s="3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="L3" s="6" t="inlineStr">
+      <c r="L2" s="3" t="inlineStr">
         <is>
           <t>x</t>
         </is>
       </c>
-      <c r="M3" s="6" t="inlineStr"/>
-      <c r="N3" s="6" t="inlineStr"/>
-      <c r="O3" s="6" t="inlineStr"/>
-      <c r="P3" s="6" t="inlineStr"/>
-      <c r="Q3" s="6" t="inlineStr">
+      <c r="M2" s="3" t="inlineStr"/>
+      <c r="N2" s="3" t="inlineStr"/>
+      <c r="O2" s="3" t="inlineStr"/>
+      <c r="P2" s="3" t="inlineStr"/>
+      <c r="Q2" s="3" t="inlineStr">
         <is>
           <t>Macro outdoor</t>
         </is>
       </c>
-      <c r="R3" s="6" t="inlineStr">
+      <c r="R2" s="3" t="inlineStr">
         <is>
           <t>MBF HOST</t>
         </is>
       </c>
-      <c r="S3" s="6" t="inlineStr">
+      <c r="S2" s="3" t="inlineStr">
         <is>
           <t>MBF HOST</t>
         </is>
       </c>
-      <c r="T3" s="6" t="inlineStr"/>
-      <c r="U3" s="6" t="inlineStr">
+      <c r="T2" s="3" t="inlineStr"/>
+      <c r="U2" s="3" t="inlineStr">
         <is>
           <t>PTM-001</t>
         </is>
       </c>
-      <c r="V3" s="6" t="n">
+      <c r="V2" s="3" t="n">
         <v>35.5</v>
       </c>
-      <c r="W3" s="6" t="n">
+      <c r="W2" s="3" t="n">
         <v>30</v>
       </c>
-      <c r="X3" s="6" t="inlineStr">
+      <c r="X2" s="3" t="inlineStr">
         <is>
           <t>So 1, Duong ABC, Quan Cau Giay, Ha Noi</t>
         </is>
       </c>
-      <c r="Y3" s="6" t="inlineStr"/>
+      <c r="Y2" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:Y1"/>
-  <mergeCells count="1">
-    <mergeCell ref="A2:Y2"/>
-  </mergeCells>
+  <dataValidations count="16">
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn: MB, MT hoặc MN" type="list">
+      <formula1>"MB,MT,MN"</formula1>
+    </dataValidation>
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn: VIP hoặc VVIP" type="list">
+      <formula1>"VIP,VVIP"</formula1>
+    </dataValidation>
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị ngoài phạm vi" error="Latitude phải trong khoảng 8.33–23.39 (Việt Nam)" type="decimal" errorStyle="warning" operator="between">
+      <formula1>8.33</formula1>
+      <formula2>23.39</formula2>
+    </dataValidation>
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị ngoài phạm vi" error="Longitude phải trong khoảng 102.14–109.47 (Việt Nam)" type="decimal" errorStyle="warning" operator="between">
+      <formula1>102.14</formula1>
+      <formula2>109.47</formula2>
+    </dataValidation>
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Nhập &quot;x&quot; nếu có, để trống nếu không" type="list">
+      <formula1>"x,"</formula1>
+    </dataValidation>
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Nhập &quot;x&quot; nếu có, để trống nếu không" type="list">
+      <formula1>"x,"</formula1>
+    </dataValidation>
+    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Nhập &quot;x&quot; nếu có, để trống nếu không" type="list">
+      <formula1>"x,"</formula1>
+    </dataValidation>
+    <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Nhập &quot;x&quot; nếu có, để trống nếu không" type="list">
+      <formula1>"x,"</formula1>
+    </dataValidation>
+    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Nhập &quot;x&quot; nếu có, để trống nếu không" type="list">
+      <formula1>"x,"</formula1>
+    </dataValidation>
+    <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Nhập &quot;x&quot; nếu có, để trống nếu không" type="list">
+      <formula1>"x,"</formula1>
+    </dataValidation>
+    <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Nhập &quot;x&quot; nếu có, để trống nếu không" type="list">
+      <formula1>"x,"</formula1>
+    </dataValidation>
+    <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Nhập &quot;x&quot; nếu có, để trống nếu không" type="list">
+      <formula1>"x,"</formula1>
+    </dataValidation>
+    <dataValidation sqref="Q2:Q1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn từ danh sách phân loại trạm" type="list">
+      <formula1>"IBC,Macro outdoor,IBC + Outdoor,Smallcell,miniDAS"</formula1>
+    </dataValidation>
+    <dataValidation sqref="R2:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn: VNPT HOST hoặc MBF HOST" type="list">
+      <formula1>"VNPT HOST,MBF HOST"</formula1>
+    </dataValidation>
+    <dataValidation sqref="S2:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn: VNPT HOST hoặc MBF HOST" type="list">
+      <formula1>"VNPT HOST,MBF HOST"</formula1>
+    </dataValidation>
+    <dataValidation sqref="T2:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn: VNPT HOST hoặc MBF HOST" type="list">
+      <formula1>"VNPT HOST,MBF HOST"</formula1>
+    </dataValidation>
+  </dataValidations>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/backend/templates/template_site.xlsx
+++ b/backend/templates/template_site.xlsx
@@ -705,7 +705,7 @@
       </c>
       <c r="X2" s="3" t="inlineStr">
         <is>
-          <t>So 1, Duong ABC, Quan Cau Giay, Ha Noi</t>
+          <t>So 1, Duong ABC, Ha Noi</t>
         </is>
       </c>
       <c r="Y2" s="3" t="inlineStr"/>
@@ -713,54 +713,54 @@
   </sheetData>
   <autoFilter ref="A1:Y1"/>
   <dataValidations count="16">
-    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn: MB, MT hoặc MN" type="list">
+    <dataValidation sqref="A2:A1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"MB,MT,MN"</formula1>
     </dataValidation>
-    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn: VIP hoặc VVIP" type="list">
+    <dataValidation sqref="F2:F1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"VIP,VVIP"</formula1>
     </dataValidation>
-    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị ngoài phạm vi" error="Latitude phải trong khoảng 8.33–23.39 (Việt Nam)" type="decimal" errorStyle="warning" operator="between">
+    <dataValidation sqref="G2:G1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị ngoài phạm vi" error="Giá trị ngoài phạm vi" type="decimal" errorStyle="warning" operator="between">
       <formula1>8.33</formula1>
       <formula2>23.39</formula2>
     </dataValidation>
-    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị ngoài phạm vi" error="Longitude phải trong khoảng 102.14–109.47 (Việt Nam)" type="decimal" errorStyle="warning" operator="between">
+    <dataValidation sqref="H2:H1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị ngoài phạm vi" error="Giá trị ngoài phạm vi" type="decimal" errorStyle="warning" operator="between">
       <formula1>102.14</formula1>
       <formula2>109.47</formula2>
     </dataValidation>
-    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Nhập &quot;x&quot; nếu có, để trống nếu không" type="list">
+    <dataValidation sqref="I2:I1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"x,"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Nhập &quot;x&quot; nếu có, để trống nếu không" type="list">
+    <dataValidation sqref="J2:J1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"x,"</formula1>
     </dataValidation>
-    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Nhập &quot;x&quot; nếu có, để trống nếu không" type="list">
+    <dataValidation sqref="K2:K1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"x,"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Nhập &quot;x&quot; nếu có, để trống nếu không" type="list">
+    <dataValidation sqref="L2:L1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"x,"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Nhập &quot;x&quot; nếu có, để trống nếu không" type="list">
+    <dataValidation sqref="M2:M1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"x,"</formula1>
     </dataValidation>
-    <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Nhập &quot;x&quot; nếu có, để trống nếu không" type="list">
+    <dataValidation sqref="N2:N1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"x,"</formula1>
     </dataValidation>
-    <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Nhập &quot;x&quot; nếu có, để trống nếu không" type="list">
+    <dataValidation sqref="O2:O1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"x,"</formula1>
     </dataValidation>
-    <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Nhập &quot;x&quot; nếu có, để trống nếu không" type="list">
+    <dataValidation sqref="P2:P1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"x,"</formula1>
     </dataValidation>
-    <dataValidation sqref="Q2:Q1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn từ danh sách phân loại trạm" type="list">
+    <dataValidation sqref="Q2:Q1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"IBC,Macro outdoor,IBC + Outdoor,Smallcell,miniDAS"</formula1>
     </dataValidation>
-    <dataValidation sqref="R2:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn: VNPT HOST hoặc MBF HOST" type="list">
+    <dataValidation sqref="R2:R1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"VNPT HOST,MBF HOST"</formula1>
     </dataValidation>
-    <dataValidation sqref="S2:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn: VNPT HOST hoặc MBF HOST" type="list">
+    <dataValidation sqref="S2:S1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"VNPT HOST,MBF HOST"</formula1>
     </dataValidation>
-    <dataValidation sqref="T2:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Chọn: VNPT HOST hoặc MBF HOST" type="list">
+    <dataValidation sqref="T2:T1000" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Giá trị không hợp lệ" error="Vui lòng chọn từ danh sách" type="list">
       <formula1>"VNPT HOST,MBF HOST"</formula1>
     </dataValidation>
   </dataValidations>
